--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.10_Q20_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.10_Q20_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.009716560836943484</v>
+        <v>0.009180521102494753</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009716560836943484</v>
+        <v>0.009180521102494753</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.009131791669228709</v>
+        <v>0.008533903954698593</v>
       </c>
       <c r="C3" t="n">
-        <v>0.009131791669228709</v>
+        <v>0.008533903954698593</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.008605845624885798</v>
+        <v>0.007970777793890748</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008605845624885798</v>
+        <v>0.007970777793890748</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0084646186151957</v>
+        <v>0.007829600355421963</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0084646186151957</v>
+        <v>0.007829600355421963</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.009006122491802493</v>
+        <v>0.008327527757285215</v>
       </c>
       <c r="C6" t="n">
-        <v>0.009006122491802493</v>
+        <v>0.008327527757285215</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.01041426859184673</v>
+        <v>0.009787930039012325</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01041426859184673</v>
+        <v>0.009787930039012325</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.01297585622823641</v>
+        <v>0.01230523963701661</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01297585622823641</v>
+        <v>0.01230523963701661</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.01650853083837201</v>
+        <v>0.01574267990271429</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01650853083837201</v>
+        <v>0.01574267990271429</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.02068524101544665</v>
+        <v>0.01975895600049958</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02068524101544665</v>
+        <v>0.01975895600049958</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -581,10 +581,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.02519605873653024</v>
+        <v>0.02403376218853766</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02519605873653024</v>
+        <v>0.02403376218853766</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -595,10 +595,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.02953698736046573</v>
+        <v>0.02809182173505597</v>
       </c>
       <c r="C12" t="n">
-        <v>0.02953698736046573</v>
+        <v>0.02809182173505597</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.03426649522539388</v>
+        <v>0.03251359961633354</v>
       </c>
       <c r="C13" t="n">
-        <v>0.03426649522539388</v>
+        <v>0.03251359961633354</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0400372442523968</v>
+        <v>0.03797454555938808</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0400372442523968</v>
+        <v>0.03797454555938808</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -637,10 +637,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.04655189846831245</v>
+        <v>0.04420426488235171</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04655189846831245</v>
+        <v>0.04420426488235171</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -651,10 +651,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.05291480133064911</v>
+        <v>0.05032062287158665</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05291480133064911</v>
+        <v>0.05032062287158665</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -665,10 +665,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.05810495423510274</v>
+        <v>0.05532486595517239</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05810495423510274</v>
+        <v>0.05532486595517239</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -679,10 +679,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.06269418766895926</v>
+        <v>0.05973447014416834</v>
       </c>
       <c r="C18" t="n">
-        <v>0.06269418766895926</v>
+        <v>0.05973447014416834</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.06591204801924247</v>
+        <v>0.06281302068747244</v>
       </c>
       <c r="C19" t="n">
-        <v>0.06591204801924247</v>
+        <v>0.06281302068747244</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -707,10 +707,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.06812205843295645</v>
+        <v>0.06489567877806909</v>
       </c>
       <c r="C20" t="n">
-        <v>0.06812205843295645</v>
+        <v>0.06489567877806909</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.06903440238987156</v>
+        <v>0.06571747622325409</v>
       </c>
       <c r="C21" t="n">
-        <v>0.06903440238987156</v>
+        <v>0.06571747622325409</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -735,10 +735,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.06956607589330432</v>
+        <v>0.0661648451467953</v>
       </c>
       <c r="C22" t="n">
-        <v>0.06956607589330432</v>
+        <v>0.0661648451467953</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -749,10 +749,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.06863104220503378</v>
+        <v>0.06522615159664756</v>
       </c>
       <c r="C23" t="n">
-        <v>0.06863104220503378</v>
+        <v>0.06522615159664756</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -763,10 +763,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.06752613858543607</v>
+        <v>0.06414220935012516</v>
       </c>
       <c r="C24" t="n">
-        <v>0.06752613858543607</v>
+        <v>0.06414220935012516</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.06600868043667334</v>
+        <v>0.06269712111258272</v>
       </c>
       <c r="C25" t="n">
-        <v>0.06600868043667334</v>
+        <v>0.06269712111258272</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.06422886605504405</v>
+        <v>0.06102044726481998</v>
       </c>
       <c r="C26" t="n">
-        <v>0.06422886605504405</v>
+        <v>0.06102044726481998</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -805,10 +805,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.06290664362424314</v>
+        <v>0.05976715204842162</v>
       </c>
       <c r="C27" t="n">
-        <v>0.06290664362424314</v>
+        <v>0.05976715204842162</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -819,10 +819,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.0599554724260377</v>
+        <v>0.05699480763336892</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0599554724260377</v>
+        <v>0.05699480763336892</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -833,10 +833,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.05839588092100705</v>
+        <v>0.05552446923048299</v>
       </c>
       <c r="C29" t="n">
-        <v>0.05839588092100705</v>
+        <v>0.05552446923048299</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -847,10 +847,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.05785160476169394</v>
+        <v>0.05503736083823271</v>
       </c>
       <c r="C30" t="n">
-        <v>0.05785160476169394</v>
+        <v>0.05503736083823271</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -861,10 +861,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.05691013159050706</v>
+        <v>0.05415423202967064</v>
       </c>
       <c r="C31" t="n">
-        <v>0.05691013159050706</v>
+        <v>0.05415423202967064</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
